--- a/artfynd/A 24591-2026 artfynd.xlsx
+++ b/artfynd/A 24591-2026 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134206267</v>
+        <v>134213092</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>78363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481688</v>
+        <v>481817</v>
       </c>
       <c r="R5" t="n">
-        <v>6950157</v>
+        <v>6949854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134213092</v>
+        <v>134206267</v>
       </c>
       <c r="B6" t="n">
-        <v>78363</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481817</v>
+        <v>481688</v>
       </c>
       <c r="R6" t="n">
-        <v>6949854</v>
+        <v>6950157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134213357</v>
+        <v>134213437</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>79025</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481817</v>
+        <v>481808</v>
       </c>
       <c r="R12" t="n">
-        <v>6949854</v>
+        <v>6949875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134213437</v>
+        <v>134213357</v>
       </c>
       <c r="B13" t="n">
-        <v>79025</v>
+        <v>78762</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481808</v>
+        <v>481817</v>
       </c>
       <c r="R13" t="n">
-        <v>6949875</v>
+        <v>6949854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,45 +2163,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134206493</v>
+        <v>134209814</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>58349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481697</v>
+        <v>481789</v>
       </c>
       <c r="R16" t="n">
-        <v>6950091</v>
+        <v>6950042</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2238,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2248,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,50 +2275,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134209814</v>
+        <v>134206493</v>
       </c>
       <c r="B17" t="n">
-        <v>58349</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481789</v>
+        <v>481697</v>
       </c>
       <c r="R17" t="n">
-        <v>6950042</v>
+        <v>6950091</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,50 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134208455</v>
+        <v>134212431</v>
       </c>
       <c r="B20" t="n">
-        <v>58658</v>
+        <v>83344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Småbrännorna, Småbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481747</v>
+        <v>481892</v>
       </c>
       <c r="R20" t="n">
-        <v>6950122</v>
+        <v>6949705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,45 +2708,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134211814</v>
+        <v>134208455</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>58658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Småbrännorna, Småbrännorna, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481902</v>
+        <v>481747</v>
       </c>
       <c r="R21" t="n">
-        <v>6949740</v>
+        <v>6950122</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134212431</v>
+        <v>134211814</v>
       </c>
       <c r="B22" t="n">
-        <v>83344</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481892</v>
+        <v>481902</v>
       </c>
       <c r="R22" t="n">
-        <v>6949705</v>
+        <v>6949740</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,32 +2927,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134213678</v>
+        <v>134207989</v>
       </c>
       <c r="B23" t="n">
-        <v>80478</v>
+        <v>83208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481774</v>
+        <v>481723</v>
       </c>
       <c r="R23" t="n">
-        <v>6949960</v>
+        <v>6950110</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134207989</v>
+        <v>134212822</v>
       </c>
       <c r="B24" t="n">
-        <v>83208</v>
+        <v>79359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,34 +3045,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Småbrännorna, Småbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481723</v>
+        <v>481852</v>
       </c>
       <c r="R24" t="n">
-        <v>6950110</v>
+        <v>6949782</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,45 +3141,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134212822</v>
+        <v>134213678</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>80478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Småbrännorna, Småbrännorna, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481852</v>
+        <v>481774</v>
       </c>
       <c r="R25" t="n">
-        <v>6949782</v>
+        <v>6949960</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,7 +3248,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134209118</v>
+        <v>134208954</v>
       </c>
       <c r="B26" t="n">
         <v>79359</v>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481769</v>
+        <v>481741</v>
       </c>
       <c r="R26" t="n">
-        <v>6950077</v>
+        <v>6950099</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,7 +3355,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134208954</v>
+        <v>134206802</v>
       </c>
       <c r="B27" t="n">
         <v>79359</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481741</v>
+        <v>481703</v>
       </c>
       <c r="R27" t="n">
-        <v>6950099</v>
+        <v>6950036</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3569,7 +3569,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134206802</v>
+        <v>134209118</v>
       </c>
       <c r="B29" t="n">
         <v>79359</v>
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481703</v>
+        <v>481769</v>
       </c>
       <c r="R29" t="n">
-        <v>6950036</v>
+        <v>6950077</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 24591-2026 artfynd.xlsx
+++ b/artfynd/A 24591-2026 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134213092</v>
+        <v>134206267</v>
       </c>
       <c r="B5" t="n">
-        <v>78363</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481817</v>
+        <v>481688</v>
       </c>
       <c r="R5" t="n">
-        <v>6949854</v>
+        <v>6950157</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134206267</v>
+        <v>134213092</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>78370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481688</v>
+        <v>481817</v>
       </c>
       <c r="R6" t="n">
-        <v>6950157</v>
+        <v>6949854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,7 +1198,7 @@
         <v>134210440</v>
       </c>
       <c r="B7" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>134211634</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>134207854</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>134206719</v>
       </c>
       <c r="B11" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134213437</v>
+        <v>134213357</v>
       </c>
       <c r="B12" t="n">
-        <v>79025</v>
+        <v>78769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481808</v>
+        <v>481817</v>
       </c>
       <c r="R12" t="n">
-        <v>6949875</v>
+        <v>6949854</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134213357</v>
+        <v>134213437</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481817</v>
+        <v>481808</v>
       </c>
       <c r="R13" t="n">
-        <v>6949854</v>
+        <v>6949875</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,7 +1952,7 @@
         <v>134207598</v>
       </c>
       <c r="B14" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>134207295</v>
       </c>
       <c r="B15" t="n">
-        <v>83336</v>
+        <v>83343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>134206493</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>134210275</v>
       </c>
       <c r="B19" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>134212431</v>
       </c>
       <c r="B20" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,50 +2708,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134208455</v>
+        <v>134211814</v>
       </c>
       <c r="B21" t="n">
-        <v>58658</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Småbrännorna, Småbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481747</v>
+        <v>481902</v>
       </c>
       <c r="R21" t="n">
-        <v>6950122</v>
+        <v>6949740</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,45 +2815,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134211814</v>
+        <v>134208455</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>58658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Småbrännorna, Småbrännorna, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481902</v>
+        <v>481747</v>
       </c>
       <c r="R22" t="n">
-        <v>6949740</v>
+        <v>6950122</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2930,7 +2930,7 @@
         <v>134207989</v>
       </c>
       <c r="B23" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>134212822</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>134213678</v>
       </c>
       <c r="B25" t="n">
-        <v>80478</v>
+        <v>80485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>134208954</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134206802</v>
+        <v>134208608</v>
       </c>
       <c r="B27" t="n">
-        <v>79359</v>
+        <v>91967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481703</v>
+        <v>481750</v>
       </c>
       <c r="R27" t="n">
-        <v>6950036</v>
+        <v>6950128</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134208608</v>
+        <v>134206802</v>
       </c>
       <c r="B28" t="n">
-        <v>91960</v>
+        <v>79366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,21 +3473,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481750</v>
+        <v>481703</v>
       </c>
       <c r="R28" t="n">
-        <v>6950128</v>
+        <v>6950036</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,7 +3572,7 @@
         <v>134209118</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24591-2026 artfynd.xlsx
+++ b/artfynd/A 24591-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122165944</v>
+        <v>122165987</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481722</v>
+        <v>481662</v>
       </c>
       <c r="R2" t="n">
-        <v>6950149</v>
+        <v>6950056</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,53 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122165943</v>
+        <v>134207295</v>
       </c>
       <c r="B3" t="n">
-        <v>97197</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481711</v>
+        <v>481744</v>
       </c>
       <c r="R3" t="n">
-        <v>6950157</v>
+        <v>6949992</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122165942</v>
+        <v>134210440</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481867</v>
+        <v>481793</v>
       </c>
       <c r="R4" t="n">
-        <v>6949847</v>
+        <v>6949928</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134206267</v>
+        <v>134213437</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481688</v>
+        <v>481808</v>
       </c>
       <c r="R5" t="n">
-        <v>6950157</v>
+        <v>6949875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1061,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134213092</v>
+        <v>122165944</v>
       </c>
       <c r="B6" t="n">
-        <v>78370</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481817</v>
+        <v>481722</v>
       </c>
       <c r="R6" t="n">
-        <v>6949854</v>
+        <v>6950149</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,22 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>20:20</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>20:20</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134210440</v>
+        <v>134208608</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481793</v>
+        <v>481750</v>
       </c>
       <c r="R7" t="n">
-        <v>6949928</v>
+        <v>6950128</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1275,7 +1270,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134211634</v>
+        <v>134207989</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,34 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småbrännorna, Småbrännorna, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481908</v>
+        <v>481723</v>
       </c>
       <c r="R8" t="n">
-        <v>6949793</v>
+        <v>6950110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1367,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1382,7 +1377,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,53 +1404,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134212576</v>
+        <v>122165984</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småbrännorna, Småbrännorna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481885</v>
+        <v>481676</v>
       </c>
       <c r="R9" t="n">
-        <v>6949726</v>
+        <v>6950030</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1469,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134207854</v>
+        <v>134206719</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>91995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481720</v>
+        <v>481690</v>
       </c>
       <c r="R10" t="n">
-        <v>6950097</v>
+        <v>6950057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1601,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,48 +1608,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134206719</v>
+        <v>122165942</v>
       </c>
       <c r="B11" t="n">
-        <v>91988</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481690</v>
+        <v>481867</v>
       </c>
       <c r="R11" t="n">
-        <v>6950057</v>
+        <v>6949847</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1693,22 +1673,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,44 +1693,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134213357</v>
+        <v>134206267</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481817</v>
+        <v>481688</v>
       </c>
       <c r="R12" t="n">
-        <v>6949854</v>
+        <v>6950157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1775,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1785,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,32 +1812,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134213437</v>
+        <v>134206493</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481808</v>
+        <v>481697</v>
       </c>
       <c r="R13" t="n">
-        <v>6949875</v>
+        <v>6950091</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1882,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1892,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,32 +1919,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134207598</v>
+        <v>134206802</v>
       </c>
       <c r="B14" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481739</v>
+        <v>481703</v>
       </c>
       <c r="R14" t="n">
-        <v>6950038</v>
+        <v>6950036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +1989,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +1999,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,32 +2026,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134207295</v>
+        <v>134207854</v>
       </c>
       <c r="B15" t="n">
-        <v>83343</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481744</v>
+        <v>481720</v>
       </c>
       <c r="R15" t="n">
-        <v>6949992</v>
+        <v>6950097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2096,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2106,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,50 +2133,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134209814</v>
+        <v>134208954</v>
       </c>
       <c r="B16" t="n">
-        <v>58349</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481789</v>
+        <v>481741</v>
       </c>
       <c r="R16" t="n">
-        <v>6950042</v>
+        <v>6950099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2203,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2248,7 +2213,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,14 +2240,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134206493</v>
+        <v>134209118</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2310,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481697</v>
+        <v>481769</v>
       </c>
       <c r="R17" t="n">
-        <v>6950091</v>
+        <v>6950077</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2310,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2355,7 +2320,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,50 +2347,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134208604</v>
+        <v>134211634</v>
       </c>
       <c r="B18" t="n">
-        <v>5181</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Småbrännorna, Småbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481750</v>
+        <v>481908</v>
       </c>
       <c r="R18" t="n">
-        <v>6950128</v>
+        <v>6949793</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2417,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2427,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,45 +2454,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134210275</v>
+        <v>134211814</v>
       </c>
       <c r="B19" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Småbrännorna, Småbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481808</v>
+        <v>481902</v>
       </c>
       <c r="R19" t="n">
-        <v>6949951</v>
+        <v>6949740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2524,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2534,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,32 +2561,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134212431</v>
+        <v>134212822</v>
       </c>
       <c r="B20" t="n">
-        <v>83351</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481892</v>
+        <v>481852</v>
       </c>
       <c r="R20" t="n">
-        <v>6949705</v>
+        <v>6949782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2631,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2641,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134211814</v>
+        <v>134213357</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,34 +2679,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Småbrännorna, Småbrännorna, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481902</v>
+        <v>481817</v>
       </c>
       <c r="R21" t="n">
-        <v>6949740</v>
+        <v>6949854</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2738,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2748,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,50 +2775,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134208455</v>
+        <v>134212431</v>
       </c>
       <c r="B22" t="n">
-        <v>58658</v>
+        <v>83358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Småbrännorna, Småbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481747</v>
+        <v>481892</v>
       </c>
       <c r="R22" t="n">
-        <v>6950122</v>
+        <v>6949705</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2845,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2855,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134207989</v>
+        <v>134207598</v>
       </c>
       <c r="B23" t="n">
-        <v>83215</v>
+        <v>79992</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481723</v>
+        <v>481739</v>
       </c>
       <c r="R23" t="n">
-        <v>6950110</v>
+        <v>6950038</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2952,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3007,7 +2962,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134212822</v>
+        <v>134210275</v>
       </c>
       <c r="B24" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,34 +3000,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Småbrännorna, Småbrännorna, Jmt</t>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481852</v>
+        <v>481808</v>
       </c>
       <c r="R24" t="n">
-        <v>6949782</v>
+        <v>6949951</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3059,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3114,7 +3069,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,7 +3099,7 @@
         <v>134213678</v>
       </c>
       <c r="B25" t="n">
-        <v>80485</v>
+        <v>80492</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3248,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134208954</v>
+        <v>134213092</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>78377</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3283,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481741</v>
+        <v>481817</v>
       </c>
       <c r="R26" t="n">
-        <v>6950099</v>
+        <v>6949854</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3273,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3328,7 +3283,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,45 +3310,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134208608</v>
+        <v>134212576</v>
       </c>
       <c r="B27" t="n">
-        <v>91967</v>
+        <v>57972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+          <t>Småbrännorna, Småbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481750</v>
+        <v>481885</v>
       </c>
       <c r="R27" t="n">
-        <v>6950128</v>
+        <v>6949726</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3385,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3435,7 +3395,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,45 +3422,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134206802</v>
+        <v>134208604</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>5181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481703</v>
+        <v>481750</v>
       </c>
       <c r="R28" t="n">
-        <v>6950036</v>
+        <v>6950128</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3542,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3569,45 +3534,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134209118</v>
+        <v>134209814</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>58349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjurbäcken, Bjurbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481769</v>
+        <v>481789</v>
       </c>
       <c r="R29" t="n">
-        <v>6950077</v>
+        <v>6950042</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,7 +3609,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3649,7 +3619,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3673,6 +3643,312 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134208455</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bjurbäcken, Bjurbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>481747</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6950122</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122165943</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>481711</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6950157</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122165983</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>481676</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6950030</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24591-2026 artfynd.xlsx
+++ b/artfynd/A 24591-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122165987</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134207295</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134210440</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134213437</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122165944</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134208608</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134207989</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122165984</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134206719</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122165942</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134206267</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134206493</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134206802</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134207854</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134208954</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134209118</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2451,6 +2536,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134211634</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134211814</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134212822</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134213357</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2879,6 +2984,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134212431</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2986,6 +3096,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134207598</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3093,6 +3208,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134210275</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3200,6 +3320,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134213678</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3307,6 +3432,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134213092</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3419,6 +3549,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134212576</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3531,6 +3666,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134208604</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3643,6 +3783,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134209814</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3755,6 +3900,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134208455</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3852,6 +4002,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122165943</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3949,8 +4104,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122165983</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>